--- a/data/projects/56A0TXN/早期介入/交付预案/输出结果/机房机柜信息表.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/输出结果/机房机柜信息表.xlsx
@@ -481,7 +481,11 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -501,7 +505,11 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -521,7 +529,11 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -541,7 +553,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -561,11 +577,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -585,11 +597,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -609,11 +617,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
@@ -633,11 +637,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
